--- a/gstdatabase/statewise_GST_collection_2025-26.xlsx
+++ b/gstdatabase/statewise_GST_collection_2025-26.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GSTN\Krishnan Sir\Monthly Report\Mar-26\GST Statistics Downloads 31st Mar 26\Downloads\Tax Collection\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GSTN\Krishnan Sir\Monthly Report\Jul-26\GST Statistics Downloads 30th Jun 26\Downloads\Tax Collection\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AAF5E988-8235-1446-8F73-DF8E7AB823B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="GST_Revenue-All_India" sheetId="3" r:id="rId1"/>
@@ -568,21 +568,6 @@
     <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="1" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="1" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="17" fontId="1" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="17" fontId="1" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="17" fontId="1" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="17" fontId="1" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -604,6 +589,21 @@
     <xf numFmtId="1" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="1" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="1" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="17" fontId="1" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="17" fontId="1" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="17" fontId="1" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -619,12 +619,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -636,6 +630,12 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1006,78 +1006,78 @@
       <c r="C7" s="72"/>
       <c r="D7" s="72"/>
       <c r="E7" s="73"/>
-      <c r="F7" s="63">
+      <c r="F7" s="58">
         <v>45748</v>
       </c>
-      <c r="G7" s="64"/>
-      <c r="H7" s="64"/>
-      <c r="I7" s="65"/>
-      <c r="J7" s="63">
+      <c r="G7" s="59"/>
+      <c r="H7" s="59"/>
+      <c r="I7" s="60"/>
+      <c r="J7" s="58">
         <v>45778</v>
       </c>
-      <c r="K7" s="64"/>
-      <c r="L7" s="64"/>
-      <c r="M7" s="65"/>
-      <c r="N7" s="63">
+      <c r="K7" s="59"/>
+      <c r="L7" s="59"/>
+      <c r="M7" s="60"/>
+      <c r="N7" s="58">
         <v>45809</v>
       </c>
-      <c r="O7" s="64"/>
-      <c r="P7" s="64"/>
-      <c r="Q7" s="65"/>
-      <c r="R7" s="63">
+      <c r="O7" s="59"/>
+      <c r="P7" s="59"/>
+      <c r="Q7" s="60"/>
+      <c r="R7" s="58">
         <v>45839</v>
       </c>
-      <c r="S7" s="64"/>
-      <c r="T7" s="64"/>
-      <c r="U7" s="65"/>
-      <c r="V7" s="63">
+      <c r="S7" s="59"/>
+      <c r="T7" s="59"/>
+      <c r="U7" s="60"/>
+      <c r="V7" s="58">
         <v>45870</v>
       </c>
-      <c r="W7" s="64"/>
-      <c r="X7" s="64"/>
-      <c r="Y7" s="65"/>
-      <c r="Z7" s="63">
+      <c r="W7" s="59"/>
+      <c r="X7" s="59"/>
+      <c r="Y7" s="60"/>
+      <c r="Z7" s="58">
         <v>45901</v>
       </c>
-      <c r="AA7" s="64"/>
-      <c r="AB7" s="64"/>
-      <c r="AC7" s="65"/>
-      <c r="AD7" s="63">
+      <c r="AA7" s="59"/>
+      <c r="AB7" s="59"/>
+      <c r="AC7" s="60"/>
+      <c r="AD7" s="58">
         <v>45931</v>
       </c>
-      <c r="AE7" s="64"/>
-      <c r="AF7" s="64"/>
-      <c r="AG7" s="65"/>
-      <c r="AH7" s="63">
+      <c r="AE7" s="59"/>
+      <c r="AF7" s="59"/>
+      <c r="AG7" s="60"/>
+      <c r="AH7" s="58">
         <v>45962</v>
       </c>
-      <c r="AI7" s="64"/>
-      <c r="AJ7" s="64"/>
-      <c r="AK7" s="65"/>
-      <c r="AL7" s="63">
+      <c r="AI7" s="59"/>
+      <c r="AJ7" s="59"/>
+      <c r="AK7" s="60"/>
+      <c r="AL7" s="58">
         <v>45992</v>
       </c>
-      <c r="AM7" s="64"/>
-      <c r="AN7" s="64"/>
-      <c r="AO7" s="65"/>
-      <c r="AP7" s="63">
+      <c r="AM7" s="59"/>
+      <c r="AN7" s="59"/>
+      <c r="AO7" s="60"/>
+      <c r="AP7" s="58">
         <v>46023</v>
       </c>
-      <c r="AQ7" s="64"/>
-      <c r="AR7" s="64"/>
-      <c r="AS7" s="65"/>
-      <c r="AT7" s="63">
+      <c r="AQ7" s="59"/>
+      <c r="AR7" s="59"/>
+      <c r="AS7" s="60"/>
+      <c r="AT7" s="58">
         <v>46054</v>
       </c>
-      <c r="AU7" s="64"/>
-      <c r="AV7" s="64"/>
-      <c r="AW7" s="65"/>
-      <c r="AX7" s="63">
+      <c r="AU7" s="59"/>
+      <c r="AV7" s="59"/>
+      <c r="AW7" s="60"/>
+      <c r="AX7" s="58">
         <v>46082</v>
       </c>
-      <c r="AY7" s="64"/>
-      <c r="AZ7" s="64"/>
-      <c r="BA7" s="65"/>
+      <c r="AY7" s="59"/>
+      <c r="AZ7" s="59"/>
+      <c r="BA7" s="60"/>
     </row>
     <row r="8" spans="1:53" x14ac:dyDescent="0.3">
       <c r="A8" s="74"/>
@@ -2933,21 +2933,21 @@
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="AD7:AG7"/>
+    <mergeCell ref="Z7:AC7"/>
+    <mergeCell ref="V7:Y7"/>
+    <mergeCell ref="R7:U7"/>
+    <mergeCell ref="N7:Q7"/>
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="B7:E7"/>
+    <mergeCell ref="F7:I7"/>
+    <mergeCell ref="A7:A8"/>
+    <mergeCell ref="J7:M7"/>
     <mergeCell ref="AX7:BA7"/>
     <mergeCell ref="AT7:AW7"/>
     <mergeCell ref="AP7:AS7"/>
     <mergeCell ref="AL7:AO7"/>
     <mergeCell ref="AH7:AK7"/>
-    <mergeCell ref="A1:H1"/>
-    <mergeCell ref="B7:E7"/>
-    <mergeCell ref="F7:I7"/>
-    <mergeCell ref="A7:A8"/>
-    <mergeCell ref="J7:M7"/>
-    <mergeCell ref="AD7:AG7"/>
-    <mergeCell ref="Z7:AC7"/>
-    <mergeCell ref="V7:Y7"/>
-    <mergeCell ref="R7:U7"/>
-    <mergeCell ref="N7:Q7"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="50" orientation="landscape" horizontalDpi="0" verticalDpi="0"/>
@@ -3005,11 +3005,11 @@
       <c r="F1" s="10"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.3">
-      <c r="A2" s="75" t="str">
+      <c r="A2" s="79" t="str">
         <f>'GST_Revenue-All_India'!A3</f>
         <v>Data upto : 31st Mar 2026</v>
       </c>
-      <c r="B2" s="75"/>
+      <c r="B2" s="79"/>
     </row>
     <row r="3" spans="1:54" ht="18" x14ac:dyDescent="0.35">
       <c r="C3" s="1" t="s">
@@ -3022,17 +3022,17 @@
       <c r="AY3" s="43"/>
     </row>
     <row r="4" spans="1:54" x14ac:dyDescent="0.3">
-      <c r="A4" s="76" t="s">
+      <c r="A4" s="80" t="s">
         <v>52</v>
       </c>
-      <c r="B4" s="76"/>
+      <c r="B4" s="80"/>
       <c r="C4" s="1"/>
     </row>
     <row r="5" spans="1:54" x14ac:dyDescent="0.3">
-      <c r="A5" s="80" t="s">
+      <c r="A5" s="78" t="s">
         <v>43</v>
       </c>
-      <c r="B5" s="80" t="s">
+      <c r="B5" s="78" t="s">
         <v>1</v>
       </c>
       <c r="C5" s="71" t="str">
@@ -3042,82 +3042,82 @@
       <c r="D5" s="72"/>
       <c r="E5" s="72"/>
       <c r="F5" s="73"/>
-      <c r="G5" s="63">
+      <c r="G5" s="58">
         <v>45748</v>
       </c>
-      <c r="H5" s="64"/>
-      <c r="I5" s="64"/>
-      <c r="J5" s="65"/>
-      <c r="K5" s="63">
+      <c r="H5" s="59"/>
+      <c r="I5" s="59"/>
+      <c r="J5" s="60"/>
+      <c r="K5" s="58">
         <v>45778</v>
       </c>
-      <c r="L5" s="64"/>
-      <c r="M5" s="64"/>
-      <c r="N5" s="65"/>
-      <c r="O5" s="63">
+      <c r="L5" s="59"/>
+      <c r="M5" s="59"/>
+      <c r="N5" s="60"/>
+      <c r="O5" s="58">
         <v>45809</v>
       </c>
-      <c r="P5" s="64"/>
-      <c r="Q5" s="64"/>
-      <c r="R5" s="65"/>
-      <c r="S5" s="63">
+      <c r="P5" s="59"/>
+      <c r="Q5" s="59"/>
+      <c r="R5" s="60"/>
+      <c r="S5" s="58">
         <v>45839</v>
       </c>
-      <c r="T5" s="64"/>
-      <c r="U5" s="64"/>
-      <c r="V5" s="65"/>
-      <c r="W5" s="63">
+      <c r="T5" s="59"/>
+      <c r="U5" s="59"/>
+      <c r="V5" s="60"/>
+      <c r="W5" s="58">
         <v>45870</v>
       </c>
-      <c r="X5" s="64"/>
-      <c r="Y5" s="64"/>
-      <c r="Z5" s="65"/>
-      <c r="AA5" s="63">
+      <c r="X5" s="59"/>
+      <c r="Y5" s="59"/>
+      <c r="Z5" s="60"/>
+      <c r="AA5" s="58">
         <v>45901</v>
       </c>
-      <c r="AB5" s="64"/>
-      <c r="AC5" s="64"/>
-      <c r="AD5" s="65"/>
-      <c r="AE5" s="63">
+      <c r="AB5" s="59"/>
+      <c r="AC5" s="59"/>
+      <c r="AD5" s="60"/>
+      <c r="AE5" s="58">
         <v>45931</v>
       </c>
-      <c r="AF5" s="64"/>
-      <c r="AG5" s="64"/>
-      <c r="AH5" s="65"/>
-      <c r="AI5" s="63">
+      <c r="AF5" s="59"/>
+      <c r="AG5" s="59"/>
+      <c r="AH5" s="60"/>
+      <c r="AI5" s="58">
         <v>45962</v>
       </c>
-      <c r="AJ5" s="64"/>
-      <c r="AK5" s="64"/>
-      <c r="AL5" s="65"/>
-      <c r="AM5" s="63">
+      <c r="AJ5" s="59"/>
+      <c r="AK5" s="59"/>
+      <c r="AL5" s="60"/>
+      <c r="AM5" s="58">
         <v>45992</v>
       </c>
-      <c r="AN5" s="64"/>
-      <c r="AO5" s="64"/>
-      <c r="AP5" s="65"/>
-      <c r="AQ5" s="63">
+      <c r="AN5" s="59"/>
+      <c r="AO5" s="59"/>
+      <c r="AP5" s="60"/>
+      <c r="AQ5" s="58">
         <v>46023</v>
       </c>
-      <c r="AR5" s="64"/>
-      <c r="AS5" s="64"/>
-      <c r="AT5" s="65"/>
-      <c r="AU5" s="63">
+      <c r="AR5" s="59"/>
+      <c r="AS5" s="59"/>
+      <c r="AT5" s="60"/>
+      <c r="AU5" s="58">
         <v>46054</v>
       </c>
-      <c r="AV5" s="64"/>
-      <c r="AW5" s="64"/>
-      <c r="AX5" s="65"/>
-      <c r="AY5" s="63">
+      <c r="AV5" s="59"/>
+      <c r="AW5" s="59"/>
+      <c r="AX5" s="60"/>
+      <c r="AY5" s="58">
         <v>46082</v>
       </c>
-      <c r="AZ5" s="64"/>
-      <c r="BA5" s="64"/>
-      <c r="BB5" s="65"/>
+      <c r="AZ5" s="59"/>
+      <c r="BA5" s="59"/>
+      <c r="BB5" s="60"/>
     </row>
     <row r="6" spans="1:54" x14ac:dyDescent="0.3">
-      <c r="A6" s="80"/>
-      <c r="B6" s="80"/>
+      <c r="A6" s="78"/>
+      <c r="B6" s="78"/>
       <c r="C6" s="5" t="s">
         <v>2</v>
       </c>
@@ -10299,10 +10299,10 @@
       </c>
     </row>
     <row r="46" spans="1:56" s="11" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="79" t="s">
+      <c r="A46" s="77" t="s">
         <v>57</v>
       </c>
-      <c r="B46" s="79"/>
+      <c r="B46" s="77"/>
       <c r="C46" s="25">
         <f t="shared" ref="C46:E46" si="16">SUM(C7:C45)</f>
         <v>444309.47999999992</v>
@@ -10569,10 +10569,10 @@
       <c r="BC47" s="15"/>
     </row>
     <row r="48" spans="1:56" s="1" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A48" s="78" t="s">
+      <c r="A48" s="76" t="s">
         <v>53</v>
       </c>
-      <c r="B48" s="78"/>
+      <c r="B48" s="76"/>
       <c r="C48" s="25">
         <f>G48+K48+O48+S48+W48+AA48+AE48+AI48+AM48+AQ48+AU48+AY48</f>
         <v>0</v>
@@ -10792,10 +10792,10 @@
       <c r="BC49" s="15"/>
     </row>
     <row r="50" spans="1:55" x14ac:dyDescent="0.3">
-      <c r="A50" s="77" t="s">
+      <c r="A50" s="75" t="s">
         <v>45</v>
       </c>
-      <c r="B50" s="77"/>
+      <c r="B50" s="75"/>
       <c r="C50" s="16">
         <f>C48+C46</f>
         <v>444309.47999999992</v>
@@ -11094,6 +11094,13 @@
     </row>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="S5:V5"/>
+    <mergeCell ref="O5:R5"/>
+    <mergeCell ref="K5:N5"/>
+    <mergeCell ref="G5:J5"/>
+    <mergeCell ref="C5:F5"/>
     <mergeCell ref="AY5:BB5"/>
     <mergeCell ref="AU5:AX5"/>
     <mergeCell ref="A50:B50"/>
@@ -11107,13 +11114,6 @@
     <mergeCell ref="AE5:AH5"/>
     <mergeCell ref="AA5:AD5"/>
     <mergeCell ref="W5:Z5"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="S5:V5"/>
-    <mergeCell ref="O5:R5"/>
-    <mergeCell ref="K5:N5"/>
-    <mergeCell ref="G5:J5"/>
-    <mergeCell ref="C5:F5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup scale="45" fitToWidth="0" fitToHeight="0" orientation="landscape" r:id="rId1"/>
@@ -11162,12 +11162,12 @@
       <c r="E1" s="50"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.3">
-      <c r="A2" s="58" t="str">
+      <c r="A2" s="65" t="str">
         <f>'GST_Revenue-All_India'!A3</f>
         <v>Data upto : 31st Mar 2026</v>
       </c>
-      <c r="B2" s="58"/>
-      <c r="C2" s="58"/>
+      <c r="B2" s="65"/>
+      <c r="C2" s="65"/>
     </row>
     <row r="3" spans="1:54" ht="18" x14ac:dyDescent="0.35">
       <c r="C3" s="27" t="s">
@@ -11180,105 +11180,105 @@
       <c r="AY3" s="43"/>
     </row>
     <row r="4" spans="1:54" x14ac:dyDescent="0.3">
-      <c r="A4" s="59" t="s">
+      <c r="A4" s="66" t="s">
         <v>54</v>
       </c>
-      <c r="B4" s="59"/>
-      <c r="C4" s="59"/>
+      <c r="B4" s="66"/>
+      <c r="C4" s="66"/>
     </row>
     <row r="5" spans="1:54" x14ac:dyDescent="0.3">
       <c r="C5" s="27"/>
     </row>
     <row r="7" spans="1:54" x14ac:dyDescent="0.3">
-      <c r="A7" s="69" t="s">
+      <c r="A7" s="64" t="s">
         <v>43</v>
       </c>
-      <c r="B7" s="69" t="s">
+      <c r="B7" s="64" t="s">
         <v>1</v>
       </c>
-      <c r="C7" s="60" t="str">
+      <c r="C7" s="67" t="str">
         <f>'GST_Revenue-All_India'!B7</f>
         <v>Financial Year (up to the Month - Mar 2026)</v>
       </c>
-      <c r="D7" s="61"/>
-      <c r="E7" s="61"/>
-      <c r="F7" s="62"/>
-      <c r="G7" s="63">
+      <c r="D7" s="68"/>
+      <c r="E7" s="68"/>
+      <c r="F7" s="69"/>
+      <c r="G7" s="58">
         <v>45748</v>
       </c>
-      <c r="H7" s="64"/>
-      <c r="I7" s="64"/>
-      <c r="J7" s="65"/>
-      <c r="K7" s="63">
+      <c r="H7" s="59"/>
+      <c r="I7" s="59"/>
+      <c r="J7" s="60"/>
+      <c r="K7" s="58">
         <v>45778</v>
       </c>
-      <c r="L7" s="64"/>
-      <c r="M7" s="64"/>
-      <c r="N7" s="65"/>
-      <c r="O7" s="63">
+      <c r="L7" s="59"/>
+      <c r="M7" s="59"/>
+      <c r="N7" s="60"/>
+      <c r="O7" s="58">
         <v>45809</v>
       </c>
-      <c r="P7" s="64"/>
-      <c r="Q7" s="64"/>
-      <c r="R7" s="65"/>
-      <c r="S7" s="63">
+      <c r="P7" s="59"/>
+      <c r="Q7" s="59"/>
+      <c r="R7" s="60"/>
+      <c r="S7" s="58">
         <v>45839</v>
       </c>
-      <c r="T7" s="64"/>
-      <c r="U7" s="64"/>
-      <c r="V7" s="65"/>
-      <c r="W7" s="63">
+      <c r="T7" s="59"/>
+      <c r="U7" s="59"/>
+      <c r="V7" s="60"/>
+      <c r="W7" s="58">
         <v>45870</v>
       </c>
-      <c r="X7" s="64"/>
-      <c r="Y7" s="64"/>
-      <c r="Z7" s="65"/>
-      <c r="AA7" s="63">
+      <c r="X7" s="59"/>
+      <c r="Y7" s="59"/>
+      <c r="Z7" s="60"/>
+      <c r="AA7" s="58">
         <v>45901</v>
       </c>
-      <c r="AB7" s="64"/>
-      <c r="AC7" s="64"/>
-      <c r="AD7" s="65"/>
-      <c r="AE7" s="63">
+      <c r="AB7" s="59"/>
+      <c r="AC7" s="59"/>
+      <c r="AD7" s="60"/>
+      <c r="AE7" s="58">
         <v>45931</v>
       </c>
-      <c r="AF7" s="64"/>
-      <c r="AG7" s="64"/>
-      <c r="AH7" s="65"/>
-      <c r="AI7" s="63">
+      <c r="AF7" s="59"/>
+      <c r="AG7" s="59"/>
+      <c r="AH7" s="60"/>
+      <c r="AI7" s="58">
         <v>45962</v>
       </c>
-      <c r="AJ7" s="64"/>
-      <c r="AK7" s="64"/>
-      <c r="AL7" s="65"/>
-      <c r="AM7" s="63">
+      <c r="AJ7" s="59"/>
+      <c r="AK7" s="59"/>
+      <c r="AL7" s="60"/>
+      <c r="AM7" s="58">
         <v>45992</v>
       </c>
-      <c r="AN7" s="64"/>
-      <c r="AO7" s="64"/>
-      <c r="AP7" s="65"/>
-      <c r="AQ7" s="63">
+      <c r="AN7" s="59"/>
+      <c r="AO7" s="59"/>
+      <c r="AP7" s="60"/>
+      <c r="AQ7" s="58">
         <v>46023</v>
       </c>
-      <c r="AR7" s="64"/>
-      <c r="AS7" s="64"/>
-      <c r="AT7" s="65"/>
-      <c r="AU7" s="63">
+      <c r="AR7" s="59"/>
+      <c r="AS7" s="59"/>
+      <c r="AT7" s="60"/>
+      <c r="AU7" s="58">
         <v>46054</v>
       </c>
-      <c r="AV7" s="64"/>
-      <c r="AW7" s="64"/>
-      <c r="AX7" s="65"/>
-      <c r="AY7" s="63">
+      <c r="AV7" s="59"/>
+      <c r="AW7" s="59"/>
+      <c r="AX7" s="60"/>
+      <c r="AY7" s="58">
         <v>46082</v>
       </c>
-      <c r="AZ7" s="64"/>
-      <c r="BA7" s="64"/>
-      <c r="BB7" s="65"/>
+      <c r="AZ7" s="59"/>
+      <c r="BA7" s="59"/>
+      <c r="BB7" s="60"/>
     </row>
     <row r="8" spans="1:54" x14ac:dyDescent="0.3">
-      <c r="A8" s="69"/>
-      <c r="B8" s="69"/>
+      <c r="A8" s="64"/>
+      <c r="B8" s="64"/>
       <c r="C8" s="29" t="s">
         <v>2</v>
       </c>
@@ -18277,10 +18277,10 @@
       </c>
     </row>
     <row r="47" spans="1:55" x14ac:dyDescent="0.3">
-      <c r="A47" s="67" t="s">
+      <c r="A47" s="62" t="s">
         <v>55</v>
       </c>
-      <c r="B47" s="67"/>
+      <c r="B47" s="62"/>
       <c r="C47" s="13">
         <f t="shared" ref="C47:AB47" si="16">SUM(C9:C46)</f>
         <v>38740.973302419996</v>
@@ -18546,10 +18546,10 @@
       <c r="BC48" s="44"/>
     </row>
     <row r="49" spans="1:55" x14ac:dyDescent="0.3">
-      <c r="A49" s="68" t="s">
+      <c r="A49" s="63" t="s">
         <v>50</v>
       </c>
-      <c r="B49" s="68"/>
+      <c r="B49" s="63"/>
       <c r="C49" s="46">
         <f>G49+K49+O49+S49+W49+AA49+AE49+AI49+AM49+AQ49+AU49+AY49</f>
         <v>0</v>
@@ -18770,10 +18770,10 @@
       <c r="BC50" s="44"/>
     </row>
     <row r="51" spans="1:55" x14ac:dyDescent="0.3">
-      <c r="A51" s="66" t="s">
+      <c r="A51" s="61" t="s">
         <v>56</v>
       </c>
-      <c r="B51" s="66"/>
+      <c r="B51" s="61"/>
       <c r="C51" s="16">
         <f t="shared" ref="C51:I51" si="19">C49+C47</f>
         <v>38740.973302419996</v>
@@ -19106,6 +19106,13 @@
     </row>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="A2:C2"/>
+    <mergeCell ref="A4:C4"/>
+    <mergeCell ref="C7:F7"/>
+    <mergeCell ref="S7:V7"/>
+    <mergeCell ref="O7:R7"/>
+    <mergeCell ref="G7:J7"/>
+    <mergeCell ref="K7:N7"/>
     <mergeCell ref="AY7:BB7"/>
     <mergeCell ref="AU7:AX7"/>
     <mergeCell ref="A51:B51"/>
@@ -19119,13 +19126,6 @@
     <mergeCell ref="AE7:AH7"/>
     <mergeCell ref="AA7:AD7"/>
     <mergeCell ref="W7:Z7"/>
-    <mergeCell ref="A2:C2"/>
-    <mergeCell ref="A4:C4"/>
-    <mergeCell ref="C7:F7"/>
-    <mergeCell ref="S7:V7"/>
-    <mergeCell ref="O7:R7"/>
-    <mergeCell ref="G7:J7"/>
-    <mergeCell ref="K7:N7"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="67" orientation="landscape" horizontalDpi="0" verticalDpi="0"/>
